--- a/data/MK_YFINANCE_DATA_20260630.xlsx
+++ b/data/MK_YFINANCE_DATA_20260630.xlsx
@@ -25879,10 +25879,10 @@
         </is>
       </c>
       <c r="F481" t="n">
-        <v>8646.51</v>
+        <v>8632.459999999999</v>
       </c>
       <c r="G481" t="n">
-        <v>8646.51</v>
+        <v>8632.459999999999</v>
       </c>
       <c r="H481" t="n">
         <v>8416.700000000001</v>
@@ -25895,15 +25895,15 @@
       </c>
       <c r="K481" t="inlineStr">
         <is>
-          <t>349.72K</t>
+          <t>361.57K</t>
         </is>
       </c>
       <c r="L481" t="n">
-        <v>0.03</v>
+        <v>0.0283</v>
       </c>
       <c r="M481" t="inlineStr">
         <is>
-          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(12,'20260630',8646.51,8646.51,8416.7,8667.73,8220.8,'349.72K',0.03,GETDATE(),NULL);</t>
+          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(12,'20260630',8632.46,8632.46,8416.7,8667.73,8220.8,'361.57K',0.0283,GETDATE(),NULL);</t>
         </is>
       </c>
     </row>
@@ -27891,10 +27891,10 @@
         </is>
       </c>
       <c r="F519" t="n">
-        <v>1400.35</v>
+        <v>1396.59</v>
       </c>
       <c r="G519" t="n">
-        <v>1400.35</v>
+        <v>1396.59</v>
       </c>
       <c r="H519" t="n">
         <v>1356.86</v>
@@ -27907,15 +27907,15 @@
       </c>
       <c r="K519" t="inlineStr">
         <is>
-          <t>96.19K</t>
+          <t>100.94K</t>
         </is>
       </c>
       <c r="L519" t="n">
-        <v>0.0248</v>
+        <v>0.022</v>
       </c>
       <c r="M519" t="inlineStr">
         <is>
-          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(13,'20260630',1400.35,1400.35,1356.86,1404.1,1325.41,'96.19K',0.0248,GETDATE(),NULL);</t>
+          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(13,'20260630',1396.59,1396.59,1356.86,1404.1,1325.41,'100.94K',0.022,GETDATE(),NULL);</t>
         </is>
       </c>
     </row>
@@ -29952,10 +29952,10 @@
         </is>
       </c>
       <c r="F558" t="n">
-        <v>920.6</v>
+        <v>923.0599999999999</v>
       </c>
       <c r="G558" t="n">
-        <v>920.6</v>
+        <v>923.0599999999999</v>
       </c>
       <c r="H558" t="n">
         <v>925.21</v>
@@ -29968,15 +29968,15 @@
       </c>
       <c r="K558" t="inlineStr">
         <is>
-          <t>526.36K</t>
+          <t>546.73K</t>
         </is>
       </c>
       <c r="L558" t="n">
-        <v>0</v>
+        <v>0.0027</v>
       </c>
       <c r="M558" t="inlineStr">
         <is>
-          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(14,'20260630',920.6,920.6,925.21,935.27,910.3,'526.36K',0.0,GETDATE(),NULL);</t>
+          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(14,'20260630',923.06,923.06,925.21,935.27,910.3,'546.73K',0.0027,GETDATE(),NULL);</t>
         </is>
       </c>
     </row>
@@ -40262,10 +40262,10 @@
         </is>
       </c>
       <c r="F762" t="n">
-        <v>227.68</v>
+        <v>227.6</v>
       </c>
       <c r="G762" t="n">
-        <v>227.68</v>
+        <v>227.6</v>
       </c>
       <c r="H762" t="n">
         <v>226.8</v>
@@ -40280,7 +40280,7 @@
       <c r="L762" t="inlineStr"/>
       <c r="M762" t="inlineStr">
         <is>
-          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(20,'20260630',227.68,227.68,226.8,228.0,226.8,NULL,NULL,GETDATE(),NULL);</t>
+          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(20,'20260630',227.6,227.6,226.8,228.0,226.8,NULL,NULL,GETDATE(),NULL);</t>
         </is>
       </c>
     </row>
@@ -42365,10 +42365,10 @@
         </is>
       </c>
       <c r="F805" t="n">
-        <v>9.507999999999999</v>
+        <v>9.509</v>
       </c>
       <c r="G805" t="n">
-        <v>9.507999999999999</v>
+        <v>9.509</v>
       </c>
       <c r="H805" t="n">
         <v>9.494</v>
@@ -42381,11 +42381,11 @@
       </c>
       <c r="K805" t="inlineStr"/>
       <c r="L805" t="n">
-        <v>0.0024</v>
+        <v>0.0025</v>
       </c>
       <c r="M805" t="inlineStr">
         <is>
-          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(21,'20260630',9.508,9.508,9.494,9.525,9.494,NULL,0.0024,GETDATE(),NULL);</t>
+          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(21,'20260630',9.509,9.509,9.494,9.525,9.494,NULL,0.0025,GETDATE(),NULL);</t>
         </is>
       </c>
     </row>
@@ -46379,10 +46379,10 @@
         </is>
       </c>
       <c r="F887" t="n">
-        <v>70.09999999999999</v>
+        <v>70.18000000000001</v>
       </c>
       <c r="G887" t="n">
-        <v>70.09999999999999</v>
+        <v>70.18000000000001</v>
       </c>
       <c r="H887" t="n">
         <v>70.43000000000001</v>
@@ -46395,11 +46395,11 @@
       </c>
       <c r="K887" t="inlineStr"/>
       <c r="L887" t="n">
-        <v>-0.0092</v>
+        <v>-0.0081</v>
       </c>
       <c r="M887" t="inlineStr">
         <is>
-          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(23,'20260630',70.1,70.1,70.43,70.87,69.93,NULL,-0.0092,GETDATE(),NULL);</t>
+          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(23,'20260630',70.18,70.18,70.43,70.87,69.93,NULL,-0.0081,GETDATE(),NULL);</t>
         </is>
       </c>
     </row>
@@ -48546,10 +48546,10 @@
         </is>
       </c>
       <c r="F928" t="n">
-        <v>4000.4</v>
+        <v>3996.1</v>
       </c>
       <c r="G928" t="n">
-        <v>4000.4</v>
+        <v>3996.1</v>
       </c>
       <c r="H928" t="n">
         <v>4032.5</v>
@@ -48562,15 +48562,15 @@
       </c>
       <c r="K928" t="inlineStr">
         <is>
-          <t>35.75K</t>
+          <t>36.38K</t>
         </is>
       </c>
       <c r="L928" t="n">
-        <v>-0.0054</v>
+        <v>-0.0065</v>
       </c>
       <c r="M928" t="inlineStr">
         <is>
-          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(24,'20260630',4000.4,4000.4,4032.5,4036.7,3955.4,'35.75K',-0.0054,GETDATE(),NULL);</t>
+          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(24,'20260630',3996.1,3996.1,4032.5,4036.7,3955.4,'36.38K',-0.0065,GETDATE(),NULL);</t>
         </is>
       </c>
     </row>
@@ -50664,10 +50664,10 @@
         </is>
       </c>
       <c r="F968" t="n">
-        <v>70520.87</v>
+        <v>70611.10000000001</v>
       </c>
       <c r="G968" t="n">
-        <v>70520.87</v>
+        <v>70611.10000000001</v>
       </c>
       <c r="H968" t="n">
         <v>70085.60000000001</v>
@@ -50680,11 +50680,11 @@
       </c>
       <c r="K968" t="inlineStr"/>
       <c r="L968" t="n">
-        <v>0.0152</v>
+        <v>0.0165</v>
       </c>
       <c r="M968" t="inlineStr">
         <is>
-          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(25,'20260630',70520.87,70520.87,70085.6,70667.0,69302.19,NULL,0.0152,GETDATE(),NULL);</t>
+          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(25,'20260630',70611.1,70611.1,70085.6,70667.0,69302.19,NULL,0.0165,GETDATE(),NULL);</t>
         </is>
       </c>
     </row>
@@ -54789,10 +54789,10 @@
         </is>
       </c>
       <c r="F1049" t="n">
-        <v>101.39</v>
+        <v>101.36</v>
       </c>
       <c r="G1049" t="n">
-        <v>101.39</v>
+        <v>101.36</v>
       </c>
       <c r="H1049" t="n">
         <v>101.12</v>
@@ -54805,11 +54805,11 @@
       </c>
       <c r="K1049" t="inlineStr"/>
       <c r="L1049" t="n">
-        <v>0.0027</v>
+        <v>0.0024</v>
       </c>
       <c r="M1049" t="inlineStr">
         <is>
-          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(27,'20260630',101.39,101.39,101.12,101.39,101.12,NULL,0.0027,GETDATE(),NULL);</t>
+          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(27,'20260630',101.36,101.36,101.12,101.39,101.12,NULL,0.0024,GETDATE(),NULL);</t>
         </is>
       </c>
     </row>
@@ -56796,10 +56796,10 @@
         </is>
       </c>
       <c r="F1090" t="n">
-        <v>6.1875</v>
+        <v>6.186</v>
       </c>
       <c r="G1090" t="n">
-        <v>6.1875</v>
+        <v>6.186</v>
       </c>
       <c r="H1090" t="n">
         <v>6.175</v>
@@ -56812,11 +56812,11 @@
       </c>
       <c r="K1090" t="inlineStr"/>
       <c r="L1090" t="n">
-        <v>0.0148</v>
+        <v>0.0145</v>
       </c>
       <c r="M1090" t="inlineStr">
         <is>
-          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(28,'20260630',6.1875,6.1875,6.175,6.196,6.1095,NULL,0.0148,GETDATE(),NULL);</t>
+          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(28,'20260630',6.186,6.186,6.175,6.196,6.1095,NULL,0.0145,GETDATE(),NULL);</t>
         </is>
       </c>
     </row>
@@ -58803,10 +58803,10 @@
         </is>
       </c>
       <c r="F1131" t="n">
-        <v>3.167</v>
+        <v>3.173</v>
       </c>
       <c r="G1131" t="n">
-        <v>3.167</v>
+        <v>3.173</v>
       </c>
       <c r="H1131" t="n">
         <v>3.171</v>
@@ -58819,11 +58819,11 @@
       </c>
       <c r="K1131" t="inlineStr"/>
       <c r="L1131" t="n">
-        <v>-0.0044</v>
+        <v>-0.0025</v>
       </c>
       <c r="M1131" t="inlineStr">
         <is>
-          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(29,'20260630',3.167,3.167,3.171,3.179,3.159,NULL,-0.0044,GETDATE(),NULL);</t>
+          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(29,'20260630',3.173,3.173,3.171,3.179,3.159,NULL,-0.0025,GETDATE(),NULL);</t>
         </is>
       </c>
     </row>
@@ -60810,10 +60810,10 @@
         </is>
       </c>
       <c r="F1172" t="n">
-        <v>58.04</v>
+        <v>57.81</v>
       </c>
       <c r="G1172" t="n">
-        <v>58.04</v>
+        <v>57.81</v>
       </c>
       <c r="H1172" t="n">
         <v>58.77</v>
@@ -60826,11 +60826,11 @@
       </c>
       <c r="K1172" t="inlineStr"/>
       <c r="L1172" t="n">
-        <v>-0.0022</v>
+        <v>-0.0063</v>
       </c>
       <c r="M1172" t="inlineStr">
         <is>
-          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(30,'20260630',58.04,58.04,58.77,59.03,57.06,NULL,-0.0022,GETDATE(),NULL);</t>
+          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(30,'20260630',57.81,57.81,58.77,59.03,57.06,NULL,-0.0063,GETDATE(),NULL);</t>
         </is>
       </c>
     </row>

--- a/data/MK_YFINANCE_DATA_20260630.xlsx
+++ b/data/MK_YFINANCE_DATA_20260630.xlsx
@@ -25879,10 +25879,10 @@
         </is>
       </c>
       <c r="F481" t="n">
-        <v>8632.459999999999</v>
+        <v>8593.030000000001</v>
       </c>
       <c r="G481" t="n">
-        <v>8632.459999999999</v>
+        <v>8593.030000000001</v>
       </c>
       <c r="H481" t="n">
         <v>8416.700000000001</v>
@@ -25895,15 +25895,15 @@
       </c>
       <c r="K481" t="inlineStr">
         <is>
-          <t>361.57K</t>
+          <t>366.14K</t>
         </is>
       </c>
       <c r="L481" t="n">
-        <v>0.0283</v>
+        <v>0.0236</v>
       </c>
       <c r="M481" t="inlineStr">
         <is>
-          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(12,'20260630',8632.46,8632.46,8416.7,8667.73,8220.8,'361.57K',0.0283,GETDATE(),NULL);</t>
+          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(12,'20260630',8593.03,8593.03,8416.7,8667.73,8220.8,'366.14K',0.0236,GETDATE(),NULL);</t>
         </is>
       </c>
     </row>
@@ -27891,10 +27891,10 @@
         </is>
       </c>
       <c r="F519" t="n">
-        <v>1396.59</v>
+        <v>1390.62</v>
       </c>
       <c r="G519" t="n">
-        <v>1396.59</v>
+        <v>1390.62</v>
       </c>
       <c r="H519" t="n">
         <v>1356.86</v>
@@ -27907,15 +27907,15 @@
       </c>
       <c r="K519" t="inlineStr">
         <is>
-          <t>100.94K</t>
+          <t>102.88K</t>
         </is>
       </c>
       <c r="L519" t="n">
-        <v>0.022</v>
+        <v>0.0177</v>
       </c>
       <c r="M519" t="inlineStr">
         <is>
-          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(13,'20260630',1396.59,1396.59,1356.86,1404.1,1325.41,'100.94K',0.022,GETDATE(),NULL);</t>
+          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(13,'20260630',1390.62,1390.62,1356.86,1404.1,1325.41,'102.88K',0.0177,GETDATE(),NULL);</t>
         </is>
       </c>
     </row>
@@ -29952,10 +29952,10 @@
         </is>
       </c>
       <c r="F558" t="n">
-        <v>923.0599999999999</v>
+        <v>920.76</v>
       </c>
       <c r="G558" t="n">
-        <v>923.0599999999999</v>
+        <v>920.76</v>
       </c>
       <c r="H558" t="n">
         <v>925.21</v>
@@ -29968,15 +29968,15 @@
       </c>
       <c r="K558" t="inlineStr">
         <is>
-          <t>546.73K</t>
+          <t>556.89K</t>
         </is>
       </c>
       <c r="L558" t="n">
-        <v>0.0027</v>
+        <v>0.0002</v>
       </c>
       <c r="M558" t="inlineStr">
         <is>
-          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(14,'20260630',923.06,923.06,925.21,935.27,910.3,'546.73K',0.0027,GETDATE(),NULL);</t>
+          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(14,'20260630',920.76,920.76,925.21,935.27,910.3,'556.89K',0.0002,GETDATE(),NULL);</t>
         </is>
       </c>
     </row>
@@ -40213,10 +40213,10 @@
         </is>
       </c>
       <c r="F761" t="n">
-        <v>1546.3</v>
+        <v>1548.4</v>
       </c>
       <c r="G761" t="n">
-        <v>1546.3</v>
+        <v>1548.4</v>
       </c>
       <c r="H761" t="n">
         <v>1541.98</v>
@@ -40229,11 +40229,11 @@
       </c>
       <c r="K761" t="inlineStr"/>
       <c r="L761" t="n">
-        <v>0.0072</v>
+        <v>0.0086</v>
       </c>
       <c r="M761" t="inlineStr">
         <is>
-          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(19,'20260630',1546.3,1546.3,1541.98,1548.5,1540.43,NULL,0.0072,GETDATE(),NULL);</t>
+          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(19,'20260630',1548.4,1548.4,1541.98,1548.5,1540.43,NULL,0.0086,GETDATE(),NULL);</t>
         </is>
       </c>
     </row>
@@ -40262,10 +40262,10 @@
         </is>
       </c>
       <c r="F762" t="n">
-        <v>227.6</v>
+        <v>227.59</v>
       </c>
       <c r="G762" t="n">
-        <v>227.6</v>
+        <v>227.59</v>
       </c>
       <c r="H762" t="n">
         <v>226.8</v>
@@ -40280,7 +40280,7 @@
       <c r="L762" t="inlineStr"/>
       <c r="M762" t="inlineStr">
         <is>
-          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(20,'20260630',227.6,227.6,226.8,228.0,226.8,NULL,NULL,GETDATE(),NULL);</t>
+          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(20,'20260630',227.59,227.59,226.8,228.0,226.8,NULL,NULL,GETDATE(),NULL);</t>
         </is>
       </c>
     </row>
@@ -46379,10 +46379,10 @@
         </is>
       </c>
       <c r="F887" t="n">
-        <v>70.18000000000001</v>
+        <v>70.23</v>
       </c>
       <c r="G887" t="n">
-        <v>70.18000000000001</v>
+        <v>70.23</v>
       </c>
       <c r="H887" t="n">
         <v>70.43000000000001</v>
@@ -46395,11 +46395,11 @@
       </c>
       <c r="K887" t="inlineStr"/>
       <c r="L887" t="n">
-        <v>-0.0081</v>
+        <v>-0.0073</v>
       </c>
       <c r="M887" t="inlineStr">
         <is>
-          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(23,'20260630',70.18,70.18,70.43,70.87,69.93,NULL,-0.0081,GETDATE(),NULL);</t>
+          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(23,'20260630',70.23,70.23,70.43,70.87,69.93,NULL,-0.0073,GETDATE(),NULL);</t>
         </is>
       </c>
     </row>
@@ -48546,10 +48546,10 @@
         </is>
       </c>
       <c r="F928" t="n">
-        <v>3996.1</v>
+        <v>3996.4</v>
       </c>
       <c r="G928" t="n">
-        <v>3996.1</v>
+        <v>3996.4</v>
       </c>
       <c r="H928" t="n">
         <v>4032.5</v>
@@ -48562,15 +48562,15 @@
       </c>
       <c r="K928" t="inlineStr">
         <is>
-          <t>36.38K</t>
+          <t>36.76K</t>
         </is>
       </c>
       <c r="L928" t="n">
-        <v>-0.0065</v>
+        <v>-0.0064</v>
       </c>
       <c r="M928" t="inlineStr">
         <is>
-          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(24,'20260630',3996.1,3996.1,4032.5,4036.7,3955.4,'36.38K',-0.0065,GETDATE(),NULL);</t>
+          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(24,'20260630',3996.4,3996.4,4032.5,4036.7,3955.4,'36.76K',-0.0064,GETDATE(),NULL);</t>
         </is>
       </c>
     </row>
@@ -50664,10 +50664,10 @@
         </is>
       </c>
       <c r="F968" t="n">
-        <v>70611.10000000001</v>
+        <v>70646.63</v>
       </c>
       <c r="G968" t="n">
-        <v>70611.10000000001</v>
+        <v>70646.63</v>
       </c>
       <c r="H968" t="n">
         <v>70085.60000000001</v>
@@ -50680,11 +50680,11 @@
       </c>
       <c r="K968" t="inlineStr"/>
       <c r="L968" t="n">
-        <v>0.0165</v>
+        <v>0.017</v>
       </c>
       <c r="M968" t="inlineStr">
         <is>
-          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(25,'20260630',70611.1,70611.1,70085.6,70667.0,69302.19,NULL,0.0165,GETDATE(),NULL);</t>
+          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(25,'20260630',70646.63,70646.63,70085.6,70667.0,69302.19,NULL,0.017,GETDATE(),NULL);</t>
         </is>
       </c>
     </row>
@@ -54805,11 +54805,11 @@
       </c>
       <c r="K1049" t="inlineStr"/>
       <c r="L1049" t="n">
-        <v>0.0024</v>
+        <v>0.0025</v>
       </c>
       <c r="M1049" t="inlineStr">
         <is>
-          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(27,'20260630',101.36,101.36,101.12,101.39,101.12,NULL,0.0024,GETDATE(),NULL);</t>
+          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(27,'20260630',101.36,101.36,101.12,101.39,101.12,NULL,0.0025,GETDATE(),NULL);</t>
         </is>
       </c>
     </row>
@@ -56796,10 +56796,10 @@
         </is>
       </c>
       <c r="F1090" t="n">
-        <v>6.186</v>
+        <v>6.1855</v>
       </c>
       <c r="G1090" t="n">
-        <v>6.186</v>
+        <v>6.1855</v>
       </c>
       <c r="H1090" t="n">
         <v>6.175</v>
@@ -56812,11 +56812,11 @@
       </c>
       <c r="K1090" t="inlineStr"/>
       <c r="L1090" t="n">
-        <v>0.0145</v>
+        <v>0.0144</v>
       </c>
       <c r="M1090" t="inlineStr">
         <is>
-          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(28,'20260630',6.186,6.186,6.175,6.196,6.1095,NULL,0.0145,GETDATE(),NULL);</t>
+          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(28,'20260630',6.1855,6.1855,6.175,6.196,6.1095,NULL,0.0144,GETDATE(),NULL);</t>
         </is>
       </c>
     </row>
@@ -58803,10 +58803,10 @@
         </is>
       </c>
       <c r="F1131" t="n">
-        <v>3.173</v>
+        <v>3.171</v>
       </c>
       <c r="G1131" t="n">
-        <v>3.173</v>
+        <v>3.171</v>
       </c>
       <c r="H1131" t="n">
         <v>3.171</v>
@@ -58819,11 +58819,11 @@
       </c>
       <c r="K1131" t="inlineStr"/>
       <c r="L1131" t="n">
-        <v>-0.0025</v>
+        <v>-0.0031</v>
       </c>
       <c r="M1131" t="inlineStr">
         <is>
-          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(29,'20260630',3.173,3.173,3.171,3.179,3.159,NULL,-0.0025,GETDATE(),NULL);</t>
+          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(29,'20260630',3.171,3.171,3.171,3.179,3.159,NULL,-0.0031,GETDATE(),NULL);</t>
         </is>
       </c>
     </row>
@@ -60810,10 +60810,10 @@
         </is>
       </c>
       <c r="F1172" t="n">
-        <v>57.81</v>
+        <v>57.78</v>
       </c>
       <c r="G1172" t="n">
-        <v>57.81</v>
+        <v>57.78</v>
       </c>
       <c r="H1172" t="n">
         <v>58.77</v>
@@ -60826,11 +60826,11 @@
       </c>
       <c r="K1172" t="inlineStr"/>
       <c r="L1172" t="n">
-        <v>-0.0063</v>
+        <v>-0.0068</v>
       </c>
       <c r="M1172" t="inlineStr">
         <is>
-          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(30,'20260630',57.81,57.81,58.77,59.03,57.06,NULL,-0.0063,GETDATE(),NULL);</t>
+          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(30,'20260630',57.78,57.78,58.77,59.03,57.06,NULL,-0.0068,GETDATE(),NULL);</t>
         </is>
       </c>
     </row>

--- a/data/MK_YFINANCE_DATA_20260630.xlsx
+++ b/data/MK_YFINANCE_DATA_20260630.xlsx
@@ -25879,10 +25879,10 @@
         </is>
       </c>
       <c r="F481" t="n">
-        <v>8593.030000000001</v>
+        <v>8590</v>
       </c>
       <c r="G481" t="n">
-        <v>8593.030000000001</v>
+        <v>8590</v>
       </c>
       <c r="H481" t="n">
         <v>8416.700000000001</v>
@@ -25895,15 +25895,15 @@
       </c>
       <c r="K481" t="inlineStr">
         <is>
-          <t>366.14K</t>
+          <t>373.65K</t>
         </is>
       </c>
       <c r="L481" t="n">
-        <v>0.0236</v>
+        <v>0.0233</v>
       </c>
       <c r="M481" t="inlineStr">
         <is>
-          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(12,'20260630',8593.03,8593.03,8416.7,8667.73,8220.8,'366.14K',0.0236,GETDATE(),NULL);</t>
+          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(12,'20260630',8590.0,8590.0,8416.7,8667.73,8220.8,'373.65K',0.0233,GETDATE(),NULL);</t>
         </is>
       </c>
     </row>
@@ -27891,10 +27891,10 @@
         </is>
       </c>
       <c r="F519" t="n">
-        <v>1390.62</v>
+        <v>1390.51</v>
       </c>
       <c r="G519" t="n">
-        <v>1390.62</v>
+        <v>1390.51</v>
       </c>
       <c r="H519" t="n">
         <v>1356.86</v>
@@ -27907,15 +27907,15 @@
       </c>
       <c r="K519" t="inlineStr">
         <is>
-          <t>102.88K</t>
+          <t>106.49K</t>
         </is>
       </c>
       <c r="L519" t="n">
-        <v>0.0177</v>
+        <v>0.0176</v>
       </c>
       <c r="M519" t="inlineStr">
         <is>
-          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(13,'20260630',1390.62,1390.62,1356.86,1404.1,1325.41,'102.88K',0.0177,GETDATE(),NULL);</t>
+          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(13,'20260630',1390.51,1390.51,1356.86,1404.1,1325.41,'106.49K',0.0176,GETDATE(),NULL);</t>
         </is>
       </c>
     </row>
@@ -29952,10 +29952,10 @@
         </is>
       </c>
       <c r="F558" t="n">
-        <v>920.76</v>
+        <v>921.3200000000001</v>
       </c>
       <c r="G558" t="n">
-        <v>920.76</v>
+        <v>921.3200000000001</v>
       </c>
       <c r="H558" t="n">
         <v>925.21</v>
@@ -29968,15 +29968,15 @@
       </c>
       <c r="K558" t="inlineStr">
         <is>
-          <t>556.89K</t>
+          <t>572.99K</t>
         </is>
       </c>
       <c r="L558" t="n">
-        <v>0.0002</v>
+        <v>0.0008</v>
       </c>
       <c r="M558" t="inlineStr">
         <is>
-          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(14,'20260630',920.76,920.76,925.21,935.27,910.3,'556.89K',0.0002,GETDATE(),NULL);</t>
+          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(14,'20260630',921.32,921.32,925.21,935.27,910.3,'572.99K',0.0008,GETDATE(),NULL);</t>
         </is>
       </c>
     </row>
@@ -40262,10 +40262,10 @@
         </is>
       </c>
       <c r="F762" t="n">
-        <v>227.59</v>
+        <v>227.9</v>
       </c>
       <c r="G762" t="n">
-        <v>227.59</v>
+        <v>227.9</v>
       </c>
       <c r="H762" t="n">
         <v>226.8</v>
@@ -40280,7 +40280,7 @@
       <c r="L762" t="inlineStr"/>
       <c r="M762" t="inlineStr">
         <is>
-          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(20,'20260630',227.59,227.59,226.8,228.0,226.8,NULL,NULL,GETDATE(),NULL);</t>
+          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(20,'20260630',227.9,227.9,226.8,228.0,226.8,NULL,NULL,GETDATE(),NULL);</t>
         </is>
       </c>
     </row>
@@ -42365,10 +42365,10 @@
         </is>
       </c>
       <c r="F805" t="n">
-        <v>9.509</v>
+        <v>9.519</v>
       </c>
       <c r="G805" t="n">
-        <v>9.509</v>
+        <v>9.519</v>
       </c>
       <c r="H805" t="n">
         <v>9.494</v>
@@ -42381,11 +42381,11 @@
       </c>
       <c r="K805" t="inlineStr"/>
       <c r="L805" t="n">
-        <v>0.0025</v>
+        <v>0.0036</v>
       </c>
       <c r="M805" t="inlineStr">
         <is>
-          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(21,'20260630',9.509,9.509,9.494,9.525,9.494,NULL,0.0025,GETDATE(),NULL);</t>
+          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(21,'20260630',9.519,9.519,9.494,9.525,9.494,NULL,0.0036,GETDATE(),NULL);</t>
         </is>
       </c>
     </row>
@@ -46379,10 +46379,10 @@
         </is>
       </c>
       <c r="F887" t="n">
-        <v>70.23</v>
+        <v>70.27</v>
       </c>
       <c r="G887" t="n">
-        <v>70.23</v>
+        <v>70.27</v>
       </c>
       <c r="H887" t="n">
         <v>70.43000000000001</v>
@@ -46395,11 +46395,11 @@
       </c>
       <c r="K887" t="inlineStr"/>
       <c r="L887" t="n">
-        <v>-0.0073</v>
+        <v>-0.0068</v>
       </c>
       <c r="M887" t="inlineStr">
         <is>
-          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(23,'20260630',70.23,70.23,70.43,70.87,69.93,NULL,-0.0073,GETDATE(),NULL);</t>
+          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(23,'20260630',70.27,70.27,70.43,70.87,69.93,NULL,-0.0068,GETDATE(),NULL);</t>
         </is>
       </c>
     </row>
@@ -48546,10 +48546,10 @@
         </is>
       </c>
       <c r="F928" t="n">
-        <v>3996.4</v>
+        <v>3998.4</v>
       </c>
       <c r="G928" t="n">
-        <v>3996.4</v>
+        <v>3998.4</v>
       </c>
       <c r="H928" t="n">
         <v>4032.5</v>
@@ -48562,15 +48562,15 @@
       </c>
       <c r="K928" t="inlineStr">
         <is>
-          <t>36.76K</t>
+          <t>37.46K</t>
         </is>
       </c>
       <c r="L928" t="n">
-        <v>-0.0064</v>
+        <v>-0.0059</v>
       </c>
       <c r="M928" t="inlineStr">
         <is>
-          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(24,'20260630',3996.4,3996.4,4032.5,4036.7,3955.4,'36.76K',-0.0064,GETDATE(),NULL);</t>
+          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(24,'20260630',3998.4,3998.4,4032.5,4036.7,3955.4,'37.46K',-0.0059,GETDATE(),NULL);</t>
         </is>
       </c>
     </row>
@@ -50664,10 +50664,10 @@
         </is>
       </c>
       <c r="F968" t="n">
-        <v>70646.63</v>
+        <v>70396.28</v>
       </c>
       <c r="G968" t="n">
-        <v>70646.63</v>
+        <v>70396.28</v>
       </c>
       <c r="H968" t="n">
         <v>70085.60000000001</v>
@@ -50680,11 +50680,11 @@
       </c>
       <c r="K968" t="inlineStr"/>
       <c r="L968" t="n">
-        <v>0.017</v>
+        <v>0.0134</v>
       </c>
       <c r="M968" t="inlineStr">
         <is>
-          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(25,'20260630',70646.63,70646.63,70085.6,70667.0,69302.19,NULL,0.017,GETDATE(),NULL);</t>
+          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(25,'20260630',70396.28,70396.28,70085.6,70667.0,69302.19,NULL,0.0134,GETDATE(),NULL);</t>
         </is>
       </c>
     </row>
@@ -56796,10 +56796,10 @@
         </is>
       </c>
       <c r="F1090" t="n">
-        <v>6.1855</v>
+        <v>6.1885</v>
       </c>
       <c r="G1090" t="n">
-        <v>6.1855</v>
+        <v>6.1885</v>
       </c>
       <c r="H1090" t="n">
         <v>6.175</v>
@@ -56812,11 +56812,11 @@
       </c>
       <c r="K1090" t="inlineStr"/>
       <c r="L1090" t="n">
-        <v>0.0144</v>
+        <v>0.0149</v>
       </c>
       <c r="M1090" t="inlineStr">
         <is>
-          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(28,'20260630',6.1855,6.1855,6.175,6.196,6.1095,NULL,0.0144,GETDATE(),NULL);</t>
+          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(28,'20260630',6.1885,6.1885,6.175,6.196,6.1095,NULL,0.0149,GETDATE(),NULL);</t>
         </is>
       </c>
     </row>
@@ -58803,10 +58803,10 @@
         </is>
       </c>
       <c r="F1131" t="n">
-        <v>3.171</v>
+        <v>3.17</v>
       </c>
       <c r="G1131" t="n">
-        <v>3.171</v>
+        <v>3.17</v>
       </c>
       <c r="H1131" t="n">
         <v>3.171</v>
@@ -58819,11 +58819,11 @@
       </c>
       <c r="K1131" t="inlineStr"/>
       <c r="L1131" t="n">
-        <v>-0.0031</v>
+        <v>-0.0035</v>
       </c>
       <c r="M1131" t="inlineStr">
         <is>
-          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(29,'20260630',3.171,3.171,3.171,3.179,3.159,NULL,-0.0031,GETDATE(),NULL);</t>
+          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(29,'20260630',3.17,3.17,3.171,3.179,3.159,NULL,-0.0035,GETDATE(),NULL);</t>
         </is>
       </c>
     </row>
@@ -60810,10 +60810,10 @@
         </is>
       </c>
       <c r="F1172" t="n">
-        <v>57.78</v>
+        <v>57.97</v>
       </c>
       <c r="G1172" t="n">
-        <v>57.78</v>
+        <v>57.97</v>
       </c>
       <c r="H1172" t="n">
         <v>58.77</v>
@@ -60826,11 +60826,11 @@
       </c>
       <c r="K1172" t="inlineStr"/>
       <c r="L1172" t="n">
-        <v>-0.0068</v>
+        <v>-0.0034</v>
       </c>
       <c r="M1172" t="inlineStr">
         <is>
-          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(30,'20260630',57.78,57.78,58.77,59.03,57.06,NULL,-0.0068,GETDATE(),NULL);</t>
+          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(30,'20260630',57.97,57.97,58.77,59.03,57.06,NULL,-0.0034,GETDATE(),NULL);</t>
         </is>
       </c>
     </row>

--- a/data/MK_YFINANCE_DATA_20260630.xlsx
+++ b/data/MK_YFINANCE_DATA_20260630.xlsx
@@ -25879,10 +25879,10 @@
         </is>
       </c>
       <c r="F481" t="n">
-        <v>8590</v>
+        <v>8541.01</v>
       </c>
       <c r="G481" t="n">
-        <v>8590</v>
+        <v>8541.01</v>
       </c>
       <c r="H481" t="n">
         <v>8416.700000000001</v>
@@ -25895,15 +25895,15 @@
       </c>
       <c r="K481" t="inlineStr">
         <is>
-          <t>373.65K</t>
+          <t>378.94K</t>
         </is>
       </c>
       <c r="L481" t="n">
-        <v>0.0233</v>
+        <v>0.0174</v>
       </c>
       <c r="M481" t="inlineStr">
         <is>
-          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(12,'20260630',8590.0,8590.0,8416.7,8667.73,8220.8,'373.65K',0.0233,GETDATE(),NULL);</t>
+          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(12,'20260630',8541.01,8541.01,8416.7,8667.73,8220.8,'378.94K',0.0174,GETDATE(),NULL);</t>
         </is>
       </c>
     </row>
@@ -27891,10 +27891,10 @@
         </is>
       </c>
       <c r="F519" t="n">
-        <v>1390.51</v>
+        <v>1381.96</v>
       </c>
       <c r="G519" t="n">
-        <v>1390.51</v>
+        <v>1381.96</v>
       </c>
       <c r="H519" t="n">
         <v>1356.86</v>
@@ -27907,15 +27907,15 @@
       </c>
       <c r="K519" t="inlineStr">
         <is>
-          <t>106.49K</t>
+          <t>108.23K</t>
         </is>
       </c>
       <c r="L519" t="n">
-        <v>0.0176</v>
+        <v>0.0113</v>
       </c>
       <c r="M519" t="inlineStr">
         <is>
-          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(13,'20260630',1390.51,1390.51,1356.86,1404.1,1325.41,'106.49K',0.0176,GETDATE(),NULL);</t>
+          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(13,'20260630',1381.96,1381.96,1356.86,1404.1,1325.41,'108.23K',0.0113,GETDATE(),NULL);</t>
         </is>
       </c>
     </row>
@@ -29952,10 +29952,10 @@
         </is>
       </c>
       <c r="F558" t="n">
-        <v>921.3200000000001</v>
+        <v>918.1</v>
       </c>
       <c r="G558" t="n">
-        <v>921.3200000000001</v>
+        <v>918.1</v>
       </c>
       <c r="H558" t="n">
         <v>925.21</v>
@@ -29968,15 +29968,15 @@
       </c>
       <c r="K558" t="inlineStr">
         <is>
-          <t>572.99K</t>
+          <t>580.57K</t>
         </is>
       </c>
       <c r="L558" t="n">
-        <v>0.0008</v>
+        <v>-0.0027</v>
       </c>
       <c r="M558" t="inlineStr">
         <is>
-          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(14,'20260630',921.32,921.32,925.21,935.27,910.3,'572.99K',0.0008,GETDATE(),NULL);</t>
+          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(14,'20260630',918.1,918.1,925.21,935.27,910.3,'580.57K',-0.0027,GETDATE(),NULL);</t>
         </is>
       </c>
     </row>
@@ -40262,10 +40262,10 @@
         </is>
       </c>
       <c r="F762" t="n">
-        <v>227.9</v>
+        <v>227.96</v>
       </c>
       <c r="G762" t="n">
-        <v>227.9</v>
+        <v>227.96</v>
       </c>
       <c r="H762" t="n">
         <v>226.8</v>
@@ -40280,7 +40280,7 @@
       <c r="L762" t="inlineStr"/>
       <c r="M762" t="inlineStr">
         <is>
-          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(20,'20260630',227.9,227.9,226.8,228.0,226.8,NULL,NULL,GETDATE(),NULL);</t>
+          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(20,'20260630',227.96,227.96,226.8,228.0,226.8,NULL,NULL,GETDATE(),NULL);</t>
         </is>
       </c>
     </row>
@@ -42365,10 +42365,10 @@
         </is>
       </c>
       <c r="F805" t="n">
-        <v>9.519</v>
+        <v>9.518000000000001</v>
       </c>
       <c r="G805" t="n">
-        <v>9.519</v>
+        <v>9.518000000000001</v>
       </c>
       <c r="H805" t="n">
         <v>9.494</v>
@@ -42381,11 +42381,11 @@
       </c>
       <c r="K805" t="inlineStr"/>
       <c r="L805" t="n">
-        <v>0.0036</v>
+        <v>0.0035</v>
       </c>
       <c r="M805" t="inlineStr">
         <is>
-          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(21,'20260630',9.519,9.519,9.494,9.525,9.494,NULL,0.0036,GETDATE(),NULL);</t>
+          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(21,'20260630',9.518,9.518,9.494,9.525,9.494,NULL,0.0035,GETDATE(),NULL);</t>
         </is>
       </c>
     </row>
@@ -46379,10 +46379,10 @@
         </is>
       </c>
       <c r="F887" t="n">
-        <v>70.27</v>
+        <v>70.31</v>
       </c>
       <c r="G887" t="n">
-        <v>70.27</v>
+        <v>70.31</v>
       </c>
       <c r="H887" t="n">
         <v>70.43000000000001</v>
@@ -46395,11 +46395,11 @@
       </c>
       <c r="K887" t="inlineStr"/>
       <c r="L887" t="n">
-        <v>-0.0068</v>
+        <v>-0.0062</v>
       </c>
       <c r="M887" t="inlineStr">
         <is>
-          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(23,'20260630',70.27,70.27,70.43,70.87,69.93,NULL,-0.0068,GETDATE(),NULL);</t>
+          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(23,'20260630',70.31,70.31,70.43,70.87,69.93,NULL,-0.0062,GETDATE(),NULL);</t>
         </is>
       </c>
     </row>
@@ -48546,10 +48546,10 @@
         </is>
       </c>
       <c r="F928" t="n">
-        <v>3998.4</v>
+        <v>3994.7</v>
       </c>
       <c r="G928" t="n">
-        <v>3998.4</v>
+        <v>3994.7</v>
       </c>
       <c r="H928" t="n">
         <v>4032.5</v>
@@ -48562,15 +48562,15 @@
       </c>
       <c r="K928" t="inlineStr">
         <is>
-          <t>37.46K</t>
+          <t>37.81K</t>
         </is>
       </c>
       <c r="L928" t="n">
-        <v>-0.0059</v>
+        <v>-0.0069</v>
       </c>
       <c r="M928" t="inlineStr">
         <is>
-          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(24,'20260630',3998.4,3998.4,4032.5,4036.7,3955.4,'37.46K',-0.0059,GETDATE(),NULL);</t>
+          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(24,'20260630',3994.7,3994.7,4032.5,4036.7,3955.4,'37.81K',-0.0069,GETDATE(),NULL);</t>
         </is>
       </c>
     </row>
@@ -50664,10 +50664,10 @@
         </is>
       </c>
       <c r="F968" t="n">
-        <v>70396.28</v>
+        <v>70545.8</v>
       </c>
       <c r="G968" t="n">
-        <v>70396.28</v>
+        <v>70545.8</v>
       </c>
       <c r="H968" t="n">
         <v>70085.60000000001</v>
@@ -50680,11 +50680,11 @@
       </c>
       <c r="K968" t="inlineStr"/>
       <c r="L968" t="n">
-        <v>0.0134</v>
+        <v>0.0155</v>
       </c>
       <c r="M968" t="inlineStr">
         <is>
-          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(25,'20260630',70396.28,70396.28,70085.6,70667.0,69302.19,NULL,0.0134,GETDATE(),NULL);</t>
+          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(25,'20260630',70545.8,70545.8,70085.6,70667.0,69302.19,NULL,0.0155,GETDATE(),NULL);</t>
         </is>
       </c>
     </row>
@@ -54789,10 +54789,10 @@
         </is>
       </c>
       <c r="F1049" t="n">
-        <v>101.36</v>
+        <v>101.37</v>
       </c>
       <c r="G1049" t="n">
-        <v>101.36</v>
+        <v>101.37</v>
       </c>
       <c r="H1049" t="n">
         <v>101.12</v>
@@ -54805,11 +54805,11 @@
       </c>
       <c r="K1049" t="inlineStr"/>
       <c r="L1049" t="n">
-        <v>0.0025</v>
+        <v>0.0026</v>
       </c>
       <c r="M1049" t="inlineStr">
         <is>
-          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(27,'20260630',101.36,101.36,101.12,101.39,101.12,NULL,0.0025,GETDATE(),NULL);</t>
+          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(27,'20260630',101.37,101.37,101.12,101.39,101.12,NULL,0.0026,GETDATE(),NULL);</t>
         </is>
       </c>
     </row>
@@ -56796,10 +56796,10 @@
         </is>
       </c>
       <c r="F1090" t="n">
-        <v>6.1885</v>
+        <v>6.1795</v>
       </c>
       <c r="G1090" t="n">
-        <v>6.1885</v>
+        <v>6.1795</v>
       </c>
       <c r="H1090" t="n">
         <v>6.175</v>
@@ -56812,11 +56812,11 @@
       </c>
       <c r="K1090" t="inlineStr"/>
       <c r="L1090" t="n">
-        <v>0.0149</v>
+        <v>0.0134</v>
       </c>
       <c r="M1090" t="inlineStr">
         <is>
-          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(28,'20260630',6.1885,6.1885,6.175,6.196,6.1095,NULL,0.0149,GETDATE(),NULL);</t>
+          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(28,'20260630',6.1795,6.1795,6.175,6.196,6.1095,NULL,0.0134,GETDATE(),NULL);</t>
         </is>
       </c>
     </row>
@@ -58803,10 +58803,10 @@
         </is>
       </c>
       <c r="F1131" t="n">
-        <v>3.17</v>
+        <v>3.172</v>
       </c>
       <c r="G1131" t="n">
-        <v>3.17</v>
+        <v>3.172</v>
       </c>
       <c r="H1131" t="n">
         <v>3.171</v>
@@ -58819,11 +58819,11 @@
       </c>
       <c r="K1131" t="inlineStr"/>
       <c r="L1131" t="n">
-        <v>-0.0035</v>
+        <v>-0.0028</v>
       </c>
       <c r="M1131" t="inlineStr">
         <is>
-          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(29,'20260630',3.17,3.17,3.171,3.179,3.159,NULL,-0.0035,GETDATE(),NULL);</t>
+          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(29,'20260630',3.172,3.172,3.171,3.179,3.159,NULL,-0.0028,GETDATE(),NULL);</t>
         </is>
       </c>
     </row>
@@ -60810,10 +60810,10 @@
         </is>
       </c>
       <c r="F1172" t="n">
-        <v>57.97</v>
+        <v>57.88</v>
       </c>
       <c r="G1172" t="n">
-        <v>57.97</v>
+        <v>57.88</v>
       </c>
       <c r="H1172" t="n">
         <v>58.77</v>
@@ -60826,11 +60826,11 @@
       </c>
       <c r="K1172" t="inlineStr"/>
       <c r="L1172" t="n">
-        <v>-0.0034</v>
+        <v>-0.0052</v>
       </c>
       <c r="M1172" t="inlineStr">
         <is>
-          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(30,'20260630',57.97,57.97,58.77,59.03,57.06,NULL,-0.0034,GETDATE(),NULL);</t>
+          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(30,'20260630',57.88,57.88,58.77,59.03,57.06,NULL,-0.0052,GETDATE(),NULL);</t>
         </is>
       </c>
     </row>

--- a/data/MK_YFINANCE_DATA_20260630.xlsx
+++ b/data/MK_YFINANCE_DATA_20260630.xlsx
@@ -25879,10 +25879,10 @@
         </is>
       </c>
       <c r="F481" t="n">
-        <v>8541.01</v>
+        <v>8559.280000000001</v>
       </c>
       <c r="G481" t="n">
-        <v>8541.01</v>
+        <v>8559.280000000001</v>
       </c>
       <c r="H481" t="n">
         <v>8416.700000000001</v>
@@ -25895,15 +25895,15 @@
       </c>
       <c r="K481" t="inlineStr">
         <is>
-          <t>378.94K</t>
+          <t>384.11K</t>
         </is>
       </c>
       <c r="L481" t="n">
-        <v>0.0174</v>
+        <v>0.0196</v>
       </c>
       <c r="M481" t="inlineStr">
         <is>
-          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(12,'20260630',8541.01,8541.01,8416.7,8667.73,8220.8,'378.94K',0.0174,GETDATE(),NULL);</t>
+          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(12,'20260630',8559.28,8559.28,8416.7,8667.73,8220.8,'384.11K',0.0196,GETDATE(),NULL);</t>
         </is>
       </c>
     </row>
@@ -27891,10 +27891,10 @@
         </is>
       </c>
       <c r="F519" t="n">
-        <v>1381.96</v>
+        <v>1384.79</v>
       </c>
       <c r="G519" t="n">
-        <v>1381.96</v>
+        <v>1384.79</v>
       </c>
       <c r="H519" t="n">
         <v>1356.86</v>
@@ -27907,15 +27907,15 @@
       </c>
       <c r="K519" t="inlineStr">
         <is>
-          <t>108.23K</t>
+          <t>110.26K</t>
         </is>
       </c>
       <c r="L519" t="n">
-        <v>0.0113</v>
+        <v>0.0134</v>
       </c>
       <c r="M519" t="inlineStr">
         <is>
-          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(13,'20260630',1381.96,1381.96,1356.86,1404.1,1325.41,'108.23K',0.0113,GETDATE(),NULL);</t>
+          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(13,'20260630',1384.79,1384.79,1356.86,1404.1,1325.41,'110.26K',0.0134,GETDATE(),NULL);</t>
         </is>
       </c>
     </row>
@@ -29952,10 +29952,10 @@
         </is>
       </c>
       <c r="F558" t="n">
-        <v>918.1</v>
+        <v>920.8</v>
       </c>
       <c r="G558" t="n">
-        <v>918.1</v>
+        <v>920.8</v>
       </c>
       <c r="H558" t="n">
         <v>925.21</v>
@@ -29968,15 +29968,15 @@
       </c>
       <c r="K558" t="inlineStr">
         <is>
-          <t>580.57K</t>
+          <t>588.83K</t>
         </is>
       </c>
       <c r="L558" t="n">
-        <v>-0.0027</v>
+        <v>0.0002</v>
       </c>
       <c r="M558" t="inlineStr">
         <is>
-          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(14,'20260630',918.1,918.1,925.21,935.27,910.3,'580.57K',-0.0027,GETDATE(),NULL);</t>
+          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(14,'20260630',920.8,920.8,925.21,935.27,910.3,'588.83K',0.0002,GETDATE(),NULL);</t>
         </is>
       </c>
     </row>
@@ -40262,10 +40262,10 @@
         </is>
       </c>
       <c r="F762" t="n">
-        <v>227.96</v>
+        <v>227.95</v>
       </c>
       <c r="G762" t="n">
-        <v>227.96</v>
+        <v>227.95</v>
       </c>
       <c r="H762" t="n">
         <v>226.8</v>
@@ -40280,7 +40280,7 @@
       <c r="L762" t="inlineStr"/>
       <c r="M762" t="inlineStr">
         <is>
-          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(20,'20260630',227.96,227.96,226.8,228.0,226.8,NULL,NULL,GETDATE(),NULL);</t>
+          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(20,'20260630',227.95,227.95,226.8,228.0,226.8,NULL,NULL,GETDATE(),NULL);</t>
         </is>
       </c>
     </row>
@@ -42365,10 +42365,10 @@
         </is>
       </c>
       <c r="F805" t="n">
-        <v>9.518000000000001</v>
+        <v>9.513999999999999</v>
       </c>
       <c r="G805" t="n">
-        <v>9.518000000000001</v>
+        <v>9.513999999999999</v>
       </c>
       <c r="H805" t="n">
         <v>9.494</v>
@@ -42381,11 +42381,11 @@
       </c>
       <c r="K805" t="inlineStr"/>
       <c r="L805" t="n">
-        <v>0.0035</v>
+        <v>0.003</v>
       </c>
       <c r="M805" t="inlineStr">
         <is>
-          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(21,'20260630',9.518,9.518,9.494,9.525,9.494,NULL,0.0035,GETDATE(),NULL);</t>
+          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(21,'20260630',9.514,9.514,9.494,9.525,9.494,NULL,0.003,GETDATE(),NULL);</t>
         </is>
       </c>
     </row>
@@ -46379,10 +46379,10 @@
         </is>
       </c>
       <c r="F887" t="n">
-        <v>70.31</v>
+        <v>70.2</v>
       </c>
       <c r="G887" t="n">
-        <v>70.31</v>
+        <v>70.2</v>
       </c>
       <c r="H887" t="n">
         <v>70.43000000000001</v>
@@ -46395,11 +46395,11 @@
       </c>
       <c r="K887" t="inlineStr"/>
       <c r="L887" t="n">
-        <v>-0.0062</v>
+        <v>-0.0078</v>
       </c>
       <c r="M887" t="inlineStr">
         <is>
-          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(23,'20260630',70.31,70.31,70.43,70.87,69.93,NULL,-0.0062,GETDATE(),NULL);</t>
+          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(23,'20260630',70.2,70.2,70.43,70.87,69.93,NULL,-0.0078,GETDATE(),NULL);</t>
         </is>
       </c>
     </row>
@@ -48546,10 +48546,10 @@
         </is>
       </c>
       <c r="F928" t="n">
-        <v>3994.7</v>
+        <v>3995.3</v>
       </c>
       <c r="G928" t="n">
-        <v>3994.7</v>
+        <v>3995.3</v>
       </c>
       <c r="H928" t="n">
         <v>4032.5</v>
@@ -48562,15 +48562,15 @@
       </c>
       <c r="K928" t="inlineStr">
         <is>
-          <t>37.81K</t>
+          <t>38.04K</t>
         </is>
       </c>
       <c r="L928" t="n">
-        <v>-0.0069</v>
+        <v>-0.0067</v>
       </c>
       <c r="M928" t="inlineStr">
         <is>
-          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(24,'20260630',3994.7,3994.7,4032.5,4036.7,3955.4,'37.81K',-0.0069,GETDATE(),NULL);</t>
+          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(24,'20260630',3995.3,3995.3,4032.5,4036.7,3955.4,'38.04K',-0.0067,GETDATE(),NULL);</t>
         </is>
       </c>
     </row>
@@ -50664,10 +50664,10 @@
         </is>
       </c>
       <c r="F968" t="n">
-        <v>70545.8</v>
+        <v>70522.14</v>
       </c>
       <c r="G968" t="n">
-        <v>70545.8</v>
+        <v>70522.14</v>
       </c>
       <c r="H968" t="n">
         <v>70085.60000000001</v>
@@ -50680,11 +50680,11 @@
       </c>
       <c r="K968" t="inlineStr"/>
       <c r="L968" t="n">
-        <v>0.0155</v>
+        <v>0.0152</v>
       </c>
       <c r="M968" t="inlineStr">
         <is>
-          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(25,'20260630',70545.8,70545.8,70085.6,70667.0,69302.19,NULL,0.0155,GETDATE(),NULL);</t>
+          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(25,'20260630',70522.14,70522.14,70085.6,70667.0,69302.19,NULL,0.0152,GETDATE(),NULL);</t>
         </is>
       </c>
     </row>
@@ -54805,11 +54805,11 @@
       </c>
       <c r="K1049" t="inlineStr"/>
       <c r="L1049" t="n">
-        <v>0.0026</v>
+        <v>0.0025</v>
       </c>
       <c r="M1049" t="inlineStr">
         <is>
-          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(27,'20260630',101.37,101.37,101.12,101.39,101.12,NULL,0.0026,GETDATE(),NULL);</t>
+          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(27,'20260630',101.37,101.37,101.12,101.39,101.12,NULL,0.0025,GETDATE(),NULL);</t>
         </is>
       </c>
     </row>
@@ -56796,10 +56796,10 @@
         </is>
       </c>
       <c r="F1090" t="n">
-        <v>6.1795</v>
+        <v>6.1825</v>
       </c>
       <c r="G1090" t="n">
-        <v>6.1795</v>
+        <v>6.1825</v>
       </c>
       <c r="H1090" t="n">
         <v>6.175</v>
@@ -56812,11 +56812,11 @@
       </c>
       <c r="K1090" t="inlineStr"/>
       <c r="L1090" t="n">
-        <v>0.0134</v>
+        <v>0.0139</v>
       </c>
       <c r="M1090" t="inlineStr">
         <is>
-          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(28,'20260630',6.1795,6.1795,6.175,6.196,6.1095,NULL,0.0134,GETDATE(),NULL);</t>
+          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(28,'20260630',6.1825,6.1825,6.175,6.196,6.1095,NULL,0.0139,GETDATE(),NULL);</t>
         </is>
       </c>
     </row>
@@ -58803,10 +58803,10 @@
         </is>
       </c>
       <c r="F1131" t="n">
-        <v>3.172</v>
+        <v>3.169</v>
       </c>
       <c r="G1131" t="n">
-        <v>3.172</v>
+        <v>3.169</v>
       </c>
       <c r="H1131" t="n">
         <v>3.171</v>
@@ -58819,11 +58819,11 @@
       </c>
       <c r="K1131" t="inlineStr"/>
       <c r="L1131" t="n">
-        <v>-0.0028</v>
+        <v>-0.0038</v>
       </c>
       <c r="M1131" t="inlineStr">
         <is>
-          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(29,'20260630',3.172,3.172,3.171,3.179,3.159,NULL,-0.0028,GETDATE(),NULL);</t>
+          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(29,'20260630',3.169,3.169,3.171,3.179,3.159,NULL,-0.0038,GETDATE(),NULL);</t>
         </is>
       </c>
     </row>
@@ -60810,10 +60810,10 @@
         </is>
       </c>
       <c r="F1172" t="n">
-        <v>57.88</v>
+        <v>57.78</v>
       </c>
       <c r="G1172" t="n">
-        <v>57.88</v>
+        <v>57.78</v>
       </c>
       <c r="H1172" t="n">
         <v>58.77</v>
@@ -60826,11 +60826,11 @@
       </c>
       <c r="K1172" t="inlineStr"/>
       <c r="L1172" t="n">
-        <v>-0.0052</v>
+        <v>-0.0068</v>
       </c>
       <c r="M1172" t="inlineStr">
         <is>
-          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(30,'20260630',57.88,57.88,58.77,59.03,57.06,NULL,-0.0052,GETDATE(),NULL);</t>
+          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(30,'20260630',57.78,57.78,58.77,59.03,57.06,NULL,-0.0068,GETDATE(),NULL);</t>
         </is>
       </c>
     </row>

--- a/data/MK_YFINANCE_DATA_20260630.xlsx
+++ b/data/MK_YFINANCE_DATA_20260630.xlsx
@@ -25879,10 +25879,10 @@
         </is>
       </c>
       <c r="F481" t="n">
-        <v>8559.280000000001</v>
+        <v>8569.200000000001</v>
       </c>
       <c r="G481" t="n">
-        <v>8559.280000000001</v>
+        <v>8569.200000000001</v>
       </c>
       <c r="H481" t="n">
         <v>8416.700000000001</v>
@@ -25895,15 +25895,15 @@
       </c>
       <c r="K481" t="inlineStr">
         <is>
-          <t>384.11K</t>
+          <t>390.81K</t>
         </is>
       </c>
       <c r="L481" t="n">
-        <v>0.0196</v>
+        <v>0.0208</v>
       </c>
       <c r="M481" t="inlineStr">
         <is>
-          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(12,'20260630',8559.28,8559.28,8416.7,8667.73,8220.8,'384.11K',0.0196,GETDATE(),NULL);</t>
+          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(12,'20260630',8569.2,8569.2,8416.7,8667.73,8220.8,'390.81K',0.0208,GETDATE(),NULL);</t>
         </is>
       </c>
     </row>
@@ -27891,10 +27891,10 @@
         </is>
       </c>
       <c r="F519" t="n">
-        <v>1384.79</v>
+        <v>1386.81</v>
       </c>
       <c r="G519" t="n">
-        <v>1384.79</v>
+        <v>1386.81</v>
       </c>
       <c r="H519" t="n">
         <v>1356.86</v>
@@ -27907,15 +27907,15 @@
       </c>
       <c r="K519" t="inlineStr">
         <is>
-          <t>110.26K</t>
+          <t>112.22K</t>
         </is>
       </c>
       <c r="L519" t="n">
-        <v>0.0134</v>
+        <v>0.0149</v>
       </c>
       <c r="M519" t="inlineStr">
         <is>
-          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(13,'20260630',1384.79,1384.79,1356.86,1404.1,1325.41,'110.26K',0.0134,GETDATE(),NULL);</t>
+          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(13,'20260630',1386.81,1386.81,1356.86,1404.1,1325.41,'112.22K',0.0149,GETDATE(),NULL);</t>
         </is>
       </c>
     </row>
@@ -29952,10 +29952,10 @@
         </is>
       </c>
       <c r="F558" t="n">
-        <v>920.8</v>
+        <v>921.23</v>
       </c>
       <c r="G558" t="n">
-        <v>920.8</v>
+        <v>921.23</v>
       </c>
       <c r="H558" t="n">
         <v>925.21</v>
@@ -29968,15 +29968,15 @@
       </c>
       <c r="K558" t="inlineStr">
         <is>
-          <t>588.83K</t>
+          <t>598.22K</t>
         </is>
       </c>
       <c r="L558" t="n">
-        <v>0.0002</v>
+        <v>0.0007</v>
       </c>
       <c r="M558" t="inlineStr">
         <is>
-          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(14,'20260630',920.8,920.8,925.21,935.27,910.3,'588.83K',0.0002,GETDATE(),NULL);</t>
+          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(14,'20260630',921.23,921.23,925.21,935.27,910.3,'598.22K',0.0007,GETDATE(),NULL);</t>
         </is>
       </c>
     </row>
@@ -40213,10 +40213,10 @@
         </is>
       </c>
       <c r="F761" t="n">
-        <v>1548.4</v>
+        <v>1548.1</v>
       </c>
       <c r="G761" t="n">
-        <v>1548.4</v>
+        <v>1548.1</v>
       </c>
       <c r="H761" t="n">
         <v>1541.98</v>
@@ -40229,11 +40229,11 @@
       </c>
       <c r="K761" t="inlineStr"/>
       <c r="L761" t="n">
-        <v>0.0086</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="M761" t="inlineStr">
         <is>
-          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(19,'20260630',1548.4,1548.4,1541.98,1548.5,1540.43,NULL,0.0086,GETDATE(),NULL);</t>
+          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(19,'20260630',1548.1,1548.1,1541.98,1548.5,1540.43,NULL,0.0084,GETDATE(),NULL);</t>
         </is>
       </c>
     </row>
@@ -40262,10 +40262,10 @@
         </is>
       </c>
       <c r="F762" t="n">
-        <v>227.95</v>
+        <v>227.99</v>
       </c>
       <c r="G762" t="n">
-        <v>227.95</v>
+        <v>227.99</v>
       </c>
       <c r="H762" t="n">
         <v>226.8</v>
@@ -40280,7 +40280,7 @@
       <c r="L762" t="inlineStr"/>
       <c r="M762" t="inlineStr">
         <is>
-          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(20,'20260630',227.95,227.95,226.8,228.0,226.8,NULL,NULL,GETDATE(),NULL);</t>
+          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(20,'20260630',227.99,227.99,226.8,228.0,226.8,NULL,NULL,GETDATE(),NULL);</t>
         </is>
       </c>
     </row>
@@ -42365,10 +42365,10 @@
         </is>
       </c>
       <c r="F805" t="n">
-        <v>9.513999999999999</v>
+        <v>9.510999999999999</v>
       </c>
       <c r="G805" t="n">
-        <v>9.513999999999999</v>
+        <v>9.510999999999999</v>
       </c>
       <c r="H805" t="n">
         <v>9.494</v>
@@ -42381,11 +42381,11 @@
       </c>
       <c r="K805" t="inlineStr"/>
       <c r="L805" t="n">
-        <v>0.003</v>
+        <v>0.0027</v>
       </c>
       <c r="M805" t="inlineStr">
         <is>
-          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(21,'20260630',9.514,9.514,9.494,9.525,9.494,NULL,0.003,GETDATE(),NULL);</t>
+          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(21,'20260630',9.511,9.511,9.494,9.525,9.494,NULL,0.0027,GETDATE(),NULL);</t>
         </is>
       </c>
     </row>
@@ -46379,10 +46379,10 @@
         </is>
       </c>
       <c r="F887" t="n">
-        <v>70.2</v>
+        <v>70.01000000000001</v>
       </c>
       <c r="G887" t="n">
-        <v>70.2</v>
+        <v>70.01000000000001</v>
       </c>
       <c r="H887" t="n">
         <v>70.43000000000001</v>
@@ -46395,11 +46395,11 @@
       </c>
       <c r="K887" t="inlineStr"/>
       <c r="L887" t="n">
-        <v>-0.0078</v>
+        <v>-0.0105</v>
       </c>
       <c r="M887" t="inlineStr">
         <is>
-          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(23,'20260630',70.2,70.2,70.43,70.87,69.93,NULL,-0.0078,GETDATE(),NULL);</t>
+          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(23,'20260630',70.01,70.01,70.43,70.87,69.93,NULL,-0.0105,GETDATE(),NULL);</t>
         </is>
       </c>
     </row>
@@ -48546,10 +48546,10 @@
         </is>
       </c>
       <c r="F928" t="n">
-        <v>3995.3</v>
+        <v>3995.9</v>
       </c>
       <c r="G928" t="n">
-        <v>3995.3</v>
+        <v>3995.9</v>
       </c>
       <c r="H928" t="n">
         <v>4032.5</v>
@@ -48562,15 +48562,15 @@
       </c>
       <c r="K928" t="inlineStr">
         <is>
-          <t>38.04K</t>
+          <t>38.34K</t>
         </is>
       </c>
       <c r="L928" t="n">
-        <v>-0.0067</v>
+        <v>-0.0066</v>
       </c>
       <c r="M928" t="inlineStr">
         <is>
-          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(24,'20260630',3995.3,3995.3,4032.5,4036.7,3955.4,'38.04K',-0.0067,GETDATE(),NULL);</t>
+          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(24,'20260630',3995.9,3995.9,4032.5,4036.7,3955.4,'38.34K',-0.0066,GETDATE(),NULL);</t>
         </is>
       </c>
     </row>
@@ -50664,10 +50664,10 @@
         </is>
       </c>
       <c r="F968" t="n">
-        <v>70522.14</v>
+        <v>70431.73</v>
       </c>
       <c r="G968" t="n">
-        <v>70522.14</v>
+        <v>70431.73</v>
       </c>
       <c r="H968" t="n">
         <v>70085.60000000001</v>
@@ -50680,11 +50680,11 @@
       </c>
       <c r="K968" t="inlineStr"/>
       <c r="L968" t="n">
-        <v>0.0152</v>
+        <v>0.0139</v>
       </c>
       <c r="M968" t="inlineStr">
         <is>
-          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(25,'20260630',70522.14,70522.14,70085.6,70667.0,69302.19,NULL,0.0152,GETDATE(),NULL);</t>
+          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(25,'20260630',70431.73,70431.73,70085.6,70667.0,69302.19,NULL,0.0139,GETDATE(),NULL);</t>
         </is>
       </c>
     </row>
@@ -54789,27 +54789,27 @@
         </is>
       </c>
       <c r="F1049" t="n">
-        <v>101.37</v>
+        <v>101.42</v>
       </c>
       <c r="G1049" t="n">
-        <v>101.37</v>
+        <v>101.42</v>
       </c>
       <c r="H1049" t="n">
         <v>101.12</v>
       </c>
       <c r="I1049" t="n">
-        <v>101.39</v>
+        <v>101.43</v>
       </c>
       <c r="J1049" t="n">
         <v>101.12</v>
       </c>
       <c r="K1049" t="inlineStr"/>
       <c r="L1049" t="n">
-        <v>0.0025</v>
+        <v>0.003</v>
       </c>
       <c r="M1049" t="inlineStr">
         <is>
-          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(27,'20260630',101.37,101.37,101.12,101.39,101.12,NULL,0.0025,GETDATE(),NULL);</t>
+          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(27,'20260630',101.42,101.42,101.12,101.43,101.12,NULL,0.003,GETDATE(),NULL);</t>
         </is>
       </c>
     </row>
@@ -56796,10 +56796,10 @@
         </is>
       </c>
       <c r="F1090" t="n">
-        <v>6.1825</v>
+        <v>6.1755</v>
       </c>
       <c r="G1090" t="n">
-        <v>6.1825</v>
+        <v>6.1755</v>
       </c>
       <c r="H1090" t="n">
         <v>6.175</v>
@@ -56812,11 +56812,11 @@
       </c>
       <c r="K1090" t="inlineStr"/>
       <c r="L1090" t="n">
-        <v>0.0139</v>
+        <v>0.0128</v>
       </c>
       <c r="M1090" t="inlineStr">
         <is>
-          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(28,'20260630',6.1825,6.1825,6.175,6.196,6.1095,NULL,0.0139,GETDATE(),NULL);</t>
+          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(28,'20260630',6.1755,6.1755,6.175,6.196,6.1095,NULL,0.0128,GETDATE(),NULL);</t>
         </is>
       </c>
     </row>
@@ -58803,10 +58803,10 @@
         </is>
       </c>
       <c r="F1131" t="n">
-        <v>3.169</v>
+        <v>3.171</v>
       </c>
       <c r="G1131" t="n">
-        <v>3.169</v>
+        <v>3.171</v>
       </c>
       <c r="H1131" t="n">
         <v>3.171</v>
@@ -58819,11 +58819,11 @@
       </c>
       <c r="K1131" t="inlineStr"/>
       <c r="L1131" t="n">
-        <v>-0.0038</v>
+        <v>-0.0031</v>
       </c>
       <c r="M1131" t="inlineStr">
         <is>
-          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(29,'20260630',3.169,3.169,3.171,3.179,3.159,NULL,-0.0038,GETDATE(),NULL);</t>
+          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(29,'20260630',3.171,3.171,3.171,3.179,3.159,NULL,-0.0031,GETDATE(),NULL);</t>
         </is>
       </c>
     </row>
@@ -60810,10 +60810,10 @@
         </is>
       </c>
       <c r="F1172" t="n">
-        <v>57.78</v>
+        <v>57.79</v>
       </c>
       <c r="G1172" t="n">
-        <v>57.78</v>
+        <v>57.79</v>
       </c>
       <c r="H1172" t="n">
         <v>58.77</v>
@@ -60826,11 +60826,11 @@
       </c>
       <c r="K1172" t="inlineStr"/>
       <c r="L1172" t="n">
-        <v>-0.0068</v>
+        <v>-0.0065</v>
       </c>
       <c r="M1172" t="inlineStr">
         <is>
-          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(30,'20260630',57.78,57.78,58.77,59.03,57.06,NULL,-0.0068,GETDATE(),NULL);</t>
+          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(30,'20260630',57.79,57.79,58.77,59.03,57.06,NULL,-0.0065,GETDATE(),NULL);</t>
         </is>
       </c>
     </row>

--- a/data/MK_YFINANCE_DATA_20260630.xlsx
+++ b/data/MK_YFINANCE_DATA_20260630.xlsx
@@ -25879,10 +25879,10 @@
         </is>
       </c>
       <c r="F481" t="n">
-        <v>8569.200000000001</v>
+        <v>8563.309999999999</v>
       </c>
       <c r="G481" t="n">
-        <v>8569.200000000001</v>
+        <v>8563.309999999999</v>
       </c>
       <c r="H481" t="n">
         <v>8416.700000000001</v>
@@ -25895,15 +25895,15 @@
       </c>
       <c r="K481" t="inlineStr">
         <is>
-          <t>390.81K</t>
+          <t>400.05K</t>
         </is>
       </c>
       <c r="L481" t="n">
-        <v>0.0208</v>
+        <v>0.0201</v>
       </c>
       <c r="M481" t="inlineStr">
         <is>
-          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(12,'20260630',8569.2,8569.2,8416.7,8667.73,8220.8,'390.81K',0.0208,GETDATE(),NULL);</t>
+          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(12,'20260630',8563.31,8563.31,8416.7,8667.73,8220.8,'400.05K',0.0201,GETDATE(),NULL);</t>
         </is>
       </c>
     </row>
@@ -27891,10 +27891,10 @@
         </is>
       </c>
       <c r="F519" t="n">
-        <v>1386.81</v>
+        <v>1385.89</v>
       </c>
       <c r="G519" t="n">
-        <v>1386.81</v>
+        <v>1385.89</v>
       </c>
       <c r="H519" t="n">
         <v>1356.86</v>
@@ -27907,15 +27907,15 @@
       </c>
       <c r="K519" t="inlineStr">
         <is>
-          <t>112.22K</t>
+          <t>115.11K</t>
         </is>
       </c>
       <c r="L519" t="n">
-        <v>0.0149</v>
+        <v>0.0142</v>
       </c>
       <c r="M519" t="inlineStr">
         <is>
-          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(13,'20260630',1386.81,1386.81,1356.86,1404.1,1325.41,'112.22K',0.0149,GETDATE(),NULL);</t>
+          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(13,'20260630',1385.89,1385.89,1356.86,1404.1,1325.41,'115.11K',0.0142,GETDATE(),NULL);</t>
         </is>
       </c>
     </row>
@@ -29952,10 +29952,10 @@
         </is>
       </c>
       <c r="F558" t="n">
-        <v>921.23</v>
+        <v>920.34</v>
       </c>
       <c r="G558" t="n">
-        <v>921.23</v>
+        <v>920.34</v>
       </c>
       <c r="H558" t="n">
         <v>925.21</v>
@@ -29968,15 +29968,15 @@
       </c>
       <c r="K558" t="inlineStr">
         <is>
-          <t>598.22K</t>
+          <t>612.38K</t>
         </is>
       </c>
       <c r="L558" t="n">
-        <v>0.0007</v>
+        <v>-0.0002</v>
       </c>
       <c r="M558" t="inlineStr">
         <is>
-          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(14,'20260630',921.23,921.23,925.21,935.27,910.3,'598.22K',0.0007,GETDATE(),NULL);</t>
+          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(14,'20260630',920.34,920.34,925.21,935.27,910.3,'612.38K',-0.0002,GETDATE(),NULL);</t>
         </is>
       </c>
     </row>
@@ -40262,10 +40262,10 @@
         </is>
       </c>
       <c r="F762" t="n">
-        <v>227.99</v>
+        <v>227.97</v>
       </c>
       <c r="G762" t="n">
-        <v>227.99</v>
+        <v>227.97</v>
       </c>
       <c r="H762" t="n">
         <v>226.8</v>
@@ -40280,7 +40280,7 @@
       <c r="L762" t="inlineStr"/>
       <c r="M762" t="inlineStr">
         <is>
-          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(20,'20260630',227.99,227.99,226.8,228.0,226.8,NULL,NULL,GETDATE(),NULL);</t>
+          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(20,'20260630',227.97,227.97,226.8,228.0,226.8,NULL,NULL,GETDATE(),NULL);</t>
         </is>
       </c>
     </row>
@@ -42365,10 +42365,10 @@
         </is>
       </c>
       <c r="F805" t="n">
-        <v>9.510999999999999</v>
+        <v>9.515000000000001</v>
       </c>
       <c r="G805" t="n">
-        <v>9.510999999999999</v>
+        <v>9.515000000000001</v>
       </c>
       <c r="H805" t="n">
         <v>9.494</v>
@@ -42381,11 +42381,11 @@
       </c>
       <c r="K805" t="inlineStr"/>
       <c r="L805" t="n">
-        <v>0.0027</v>
+        <v>0.0031</v>
       </c>
       <c r="M805" t="inlineStr">
         <is>
-          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(21,'20260630',9.511,9.511,9.494,9.525,9.494,NULL,0.0027,GETDATE(),NULL);</t>
+          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(21,'20260630',9.515,9.515,9.494,9.525,9.494,NULL,0.0031,GETDATE(),NULL);</t>
         </is>
       </c>
     </row>
@@ -46379,10 +46379,10 @@
         </is>
       </c>
       <c r="F887" t="n">
-        <v>70.01000000000001</v>
+        <v>70.09</v>
       </c>
       <c r="G887" t="n">
-        <v>70.01000000000001</v>
+        <v>70.09</v>
       </c>
       <c r="H887" t="n">
         <v>70.43000000000001</v>
@@ -46395,11 +46395,11 @@
       </c>
       <c r="K887" t="inlineStr"/>
       <c r="L887" t="n">
-        <v>-0.0105</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="M887" t="inlineStr">
         <is>
-          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(23,'20260630',70.01,70.01,70.43,70.87,69.93,NULL,-0.0105,GETDATE(),NULL);</t>
+          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(23,'20260630',70.09,70.09,70.43,70.87,69.93,NULL,-0.0093,GETDATE(),NULL);</t>
         </is>
       </c>
     </row>
@@ -48546,10 +48546,10 @@
         </is>
       </c>
       <c r="F928" t="n">
-        <v>3995.9</v>
+        <v>3999.3</v>
       </c>
       <c r="G928" t="n">
-        <v>3995.9</v>
+        <v>3999.3</v>
       </c>
       <c r="H928" t="n">
         <v>4032.5</v>
@@ -48562,15 +48562,15 @@
       </c>
       <c r="K928" t="inlineStr">
         <is>
-          <t>38.34K</t>
+          <t>38.80K</t>
         </is>
       </c>
       <c r="L928" t="n">
-        <v>-0.0066</v>
+        <v>-0.0057</v>
       </c>
       <c r="M928" t="inlineStr">
         <is>
-          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(24,'20260630',3995.9,3995.9,4032.5,4036.7,3955.4,'38.34K',-0.0066,GETDATE(),NULL);</t>
+          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(24,'20260630',3999.3,3999.3,4032.5,4036.7,3955.4,'38.80K',-0.0057,GETDATE(),NULL);</t>
         </is>
       </c>
     </row>
@@ -50664,10 +50664,10 @@
         </is>
       </c>
       <c r="F968" t="n">
-        <v>70431.73</v>
+        <v>70268.8</v>
       </c>
       <c r="G968" t="n">
-        <v>70431.73</v>
+        <v>70268.8</v>
       </c>
       <c r="H968" t="n">
         <v>70085.60000000001</v>
@@ -50680,11 +50680,11 @@
       </c>
       <c r="K968" t="inlineStr"/>
       <c r="L968" t="n">
-        <v>0.0139</v>
+        <v>0.0115</v>
       </c>
       <c r="M968" t="inlineStr">
         <is>
-          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(25,'20260630',70431.73,70431.73,70085.6,70667.0,69302.19,NULL,0.0139,GETDATE(),NULL);</t>
+          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(25,'20260630',70268.8,70268.8,70085.6,70667.0,69302.19,NULL,0.0115,GETDATE(),NULL);</t>
         </is>
       </c>
     </row>
@@ -54789,10 +54789,10 @@
         </is>
       </c>
       <c r="F1049" t="n">
-        <v>101.42</v>
+        <v>101.41</v>
       </c>
       <c r="G1049" t="n">
-        <v>101.42</v>
+        <v>101.41</v>
       </c>
       <c r="H1049" t="n">
         <v>101.12</v>
@@ -54805,11 +54805,11 @@
       </c>
       <c r="K1049" t="inlineStr"/>
       <c r="L1049" t="n">
-        <v>0.003</v>
+        <v>0.0029</v>
       </c>
       <c r="M1049" t="inlineStr">
         <is>
-          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(27,'20260630',101.42,101.42,101.12,101.43,101.12,NULL,0.003,GETDATE(),NULL);</t>
+          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(27,'20260630',101.41,101.41,101.12,101.43,101.12,NULL,0.0029,GETDATE(),NULL);</t>
         </is>
       </c>
     </row>
@@ -58803,10 +58803,10 @@
         </is>
       </c>
       <c r="F1131" t="n">
-        <v>3.171</v>
+        <v>3.168</v>
       </c>
       <c r="G1131" t="n">
-        <v>3.171</v>
+        <v>3.168</v>
       </c>
       <c r="H1131" t="n">
         <v>3.171</v>
@@ -58819,11 +58819,11 @@
       </c>
       <c r="K1131" t="inlineStr"/>
       <c r="L1131" t="n">
-        <v>-0.0031</v>
+        <v>-0.0041</v>
       </c>
       <c r="M1131" t="inlineStr">
         <is>
-          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(29,'20260630',3.171,3.171,3.171,3.179,3.159,NULL,-0.0031,GETDATE(),NULL);</t>
+          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(29,'20260630',3.168,3.168,3.171,3.179,3.159,NULL,-0.0041,GETDATE(),NULL);</t>
         </is>
       </c>
     </row>
@@ -60810,10 +60810,10 @@
         </is>
       </c>
       <c r="F1172" t="n">
-        <v>57.79</v>
+        <v>57.97</v>
       </c>
       <c r="G1172" t="n">
-        <v>57.79</v>
+        <v>57.97</v>
       </c>
       <c r="H1172" t="n">
         <v>58.77</v>
@@ -60826,11 +60826,11 @@
       </c>
       <c r="K1172" t="inlineStr"/>
       <c r="L1172" t="n">
-        <v>-0.0065</v>
+        <v>-0.0036</v>
       </c>
       <c r="M1172" t="inlineStr">
         <is>
-          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(30,'20260630',57.79,57.79,58.77,59.03,57.06,NULL,-0.0065,GETDATE(),NULL);</t>
+          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(30,'20260630',57.97,57.97,58.77,59.03,57.06,NULL,-0.0036,GETDATE(),NULL);</t>
         </is>
       </c>
     </row>
